--- a/test.xlsx
+++ b/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alirachidi/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7414BE4F-6B5B-FA4C-9C87-EE8281A4C4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A50C9C-8590-6045-96C1-E35A3BB706E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2580" yWindow="600" windowWidth="20360" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>Timestamp</t>
   </si>
@@ -191,6 +191,12 @@
   </si>
   <si>
     <t>C1--20250605--00088</t>
+  </si>
+  <si>
+    <t>NONEXISTENT_IGSN</t>
+  </si>
+  <si>
+    <t>NONEXISTENT_PDV</t>
   </si>
 </sst>
 </file>
@@ -519,37 +525,37 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -854,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
@@ -1162,107 +1168,192 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:34" s="13" customFormat="1" ht="107" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+    <row r="4" spans="1:34" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>45876.768001793978</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4">
+        <v>34</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>33</v>
+      </c>
+      <c r="P4" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q4">
+        <v>-4.37</v>
+      </c>
+      <c r="T4" s="7"/>
+      <c r="U4" s="8">
+        <v>4</v>
+      </c>
+      <c r="V4">
+        <v>5</v>
+      </c>
+      <c r="X4">
+        <v>21.87</v>
+      </c>
+      <c r="Y4">
+        <v>-6.15</v>
+      </c>
+      <c r="Z4">
+        <v>21.351299999999998</v>
+      </c>
+      <c r="AA4" s="7">
+        <v>-6.1875</v>
+      </c>
+      <c r="AB4">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="AC4" s="10">
+        <v>750.59</v>
+      </c>
+      <c r="AD4" s="12"/>
+      <c r="AE4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF4" s="12"/>
+      <c r="AG4" s="10">
+        <v>6.6</v>
+      </c>
+      <c r="AH4" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" s="13" customFormat="1" ht="107" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="27" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="31" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="L4" s="23" t="s">
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="26"/>
-      <c r="U4" s="23" t="s">
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="25"/>
-      <c r="AC4" s="23" t="s">
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="31"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="33"/>
+      <c r="AC5" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="AD4" s="26"/>
-      <c r="AE4" s="23" t="s">
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="AF4" s="26"/>
-      <c r="AG4" s="27" t="s">
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="AH4" s="28"/>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
+      <c r="AH5" s="26"/>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
-      <c r="W6" s="1"/>
-      <c r="AF6" s="1"/>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
+      <c r="W7" s="1"/>
+      <c r="AF7" s="1"/>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="U5:AA5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AE5:AF5"/>
+    <mergeCell ref="AG5:AH5"/>
     <mergeCell ref="L6:Q6"/>
     <mergeCell ref="L7:Q7"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="L4:T4"/>
-    <mergeCell ref="U4:AA4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="L5:Q5"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="L5:T5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
